--- a/4 четверть_4_JavaScript_Back.xlsx
+++ b/4 четверть_4_JavaScript_Back.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40B4615-A3CD-42C2-97EA-4CC2869BF974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54AC9B4-39FD-4C48-91A6-B78EE954A272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4590" yWindow="-15945" windowWidth="23010" windowHeight="12210" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Крутой онлайн debugger" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="1013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="1015">
   <si>
     <t>Крутой онлайн debugger</t>
   </si>
@@ -17361,17 +17361,6 @@
     },
 }
 console.log(Object.values(obj).reduce((acc, el) =&gt; acc + Object.values(el).reduce((acc, el) =&gt; acc + el), 0));</t>
-  </si>
-  <si>
-    <t>const array1 = [1, 2, 3, 4];
-// 0 + 1 + 2 + 3 + 4
-const initialValue = 0;
-const sumWithInitial = array1.reduce(
-  (accumulator, currentValue) =&gt; accumulator + currentValue,
-  initialValue,
-);
-console.log(sumWithInitial);
-// Expected output: 10</t>
   </si>
   <si>
     <t>Поиск</t>
@@ -23487,6 +23476,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -23532,6 +23523,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> In order to use the export declaration in a source file, the file must be interpreted by the runtime as a module.</t>
@@ -23579,6 +23572,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t>Может быть только один на файл. Это как "лицо" модуля — то, что возвращается по умолчанию при импорте без фигурных скобок.</t>
@@ -23614,6 +23609,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> function main() {
@@ -23638,6 +23635,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> = () =&gt; {};
@@ -23660,6 +23659,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> = () =&gt; {};
@@ -23682,6 +23683,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> = 42;
@@ -23704,6 +23707,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> {}</t>
@@ -23782,6 +23787,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> = 42;
@@ -23804,6 +23811,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t>;</t>
@@ -24059,6 +24068,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t>Для агрегированного импорта следует использовать *</t>
@@ -24108,6 +24119,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Возможность 
@@ -24268,6 +24281,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t>Если бы название было index, то можно было бы импортировать :
@@ -24290,6 +24305,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -24312,6 +24329,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -24348,6 +24367,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -24433,6 +24454,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">= </t>
@@ -24454,6 +24477,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t>;</t>
@@ -24480,6 +24505,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> = </t>
@@ -24501,6 +24528,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t>('./userAuth.js');</t>
@@ -24528,6 +24557,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> = </t>
@@ -24566,6 +24597,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> = </t>
@@ -24587,6 +24620,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t>('./authMiddleware/userAuthMiddleware.js');</t>
@@ -24614,6 +24649,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> = </t>
@@ -24740,6 +24777,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -24995,16 +25034,71 @@
     MissingRequestJson
 };</t>
   </si>
+  <si>
+    <t>const array1 = [1, 2, 3, 4];
+// 0 + 1 + 2 + 3 + 4
+const initialValue = 0;
+const sumWithInitial = array1.reduce(
+  (accumulator, currentValue) =&gt; accumulator + currentValue,
+  initialValue
+);
+console.log(sumWithInitial);
+// Expected output: 10</t>
+  </si>
+  <si>
+    <t>Можно использовать вместо рекурсии</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>reduce</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - можно использовать как аналог рекурсии</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="53" x14ac:knownFonts="1">
+  <fonts count="55" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -25445,7 +25539,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -25551,6 +25645,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -25726,13 +25826,13 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -25750,164 +25850,164 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="49" fontId="24" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="49" fontId="26" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="4" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="4" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="4" borderId="9" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="4" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="4" borderId="9" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="4" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="4" borderId="9" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="4" borderId="9" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="4" borderId="12" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="4" borderId="12" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="8" borderId="9" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="8" borderId="9" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="8" borderId="10" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="8" borderId="10" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="8" borderId="11" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="8" borderId="11" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -25916,85 +26016,109 @@
     <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="15" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="15" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -26003,62 +26127,44 @@
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="14" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="13" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="16" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="16" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="17" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="16" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="16" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="17" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -26066,35 +26172,79 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="45" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="18" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="14" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="14" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="18" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="14" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="14" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="13" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="49" fontId="48" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="48" fillId="13" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="48" fillId="13" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="48" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -26102,55 +26252,17 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="14" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="14" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="14" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="14" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="14" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="14" borderId="0" xfId="4" applyFill="1"/>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="13" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="49" fontId="46" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="13" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="13" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -27183,14 +27295,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>128176</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1409698</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>1810349</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1806539</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -27225,14 +27337,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>166278</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3832338</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>1390015</xdr:rowOff>
+      <xdr:colOff>3828528</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1393825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -27267,14 +27379,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>107951</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>55411</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>918106</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>1161416</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1165226</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -27309,14 +27421,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>91514</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>54610</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2268220</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>2152552</xdr:rowOff>
+      <xdr:colOff>2264410</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>2156362</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -27351,13 +27463,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3581924</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>29845</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>4860924</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:colOff>4857114</xdr:colOff>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>1656</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -27393,14 +27505,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>139700</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>40746</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1996440</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>1768281</xdr:rowOff>
+      <xdr:colOff>2000250</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>1772091</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -27435,14 +27547,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>88901</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>636</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>400019</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>403829</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -27942,10 +28054,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="124"/>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
+      <c r="A1" s="142"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
@@ -28436,7 +28548,7 @@
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="84" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D10" s="22"/>
       <c r="F10" s="8" t="s">
@@ -28478,7 +28590,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="72" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>79</v>
       </c>
@@ -29001,7 +29113,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="116" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D63" s="8"/>
     </row>
@@ -29018,13 +29130,13 @@
     </row>
     <row r="65" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A65" s="115" t="s">
+        <v>920</v>
+      </c>
+      <c r="C65" s="115" t="s">
         <v>921</v>
       </c>
-      <c r="C65" s="115" t="s">
+      <c r="D65" s="115" t="s">
         <v>922</v>
-      </c>
-      <c r="D65" s="115" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -29301,7 +29413,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="50" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" s="9"/>
@@ -29311,41 +29423,41 @@
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="122" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D93" s="2"/>
     </row>
     <row r="94" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A94" s="122" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B94" s="122" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C94" s="122" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D94" s="2"/>
     </row>
     <row r="95" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A95" s="122" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" s="122" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="D95" s="2"/>
     </row>
     <row r="96" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A96" s="122" t="s">
+        <v>938</v>
+      </c>
+      <c r="B96" s="122" t="s">
         <v>939</v>
       </c>
-      <c r="B96" s="122" t="s">
+      <c r="C96" s="122" t="s">
         <v>940</v>
-      </c>
-      <c r="C96" s="122" t="s">
-        <v>941</v>
       </c>
       <c r="D96" s="2"/>
     </row>
@@ -29405,7 +29517,7 @@
         <v>212</v>
       </c>
       <c r="B102" s="80" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>213</v>
@@ -29535,7 +29647,7 @@
         <v>268</v>
       </c>
       <c r="D114" s="69" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="V114" s="8"/>
     </row>
@@ -29544,7 +29656,7 @@
         <v>269</v>
       </c>
       <c r="B115" s="69" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>270</v>
@@ -30841,10 +30953,10 @@
     <row r="248" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A248" s="2"/>
       <c r="B248" s="111" t="s">
+        <v>912</v>
+      </c>
+      <c r="C248" s="111" t="s">
         <v>913</v>
-      </c>
-      <c r="C248" s="111" t="s">
-        <v>914</v>
       </c>
       <c r="D248" s="2"/>
     </row>
@@ -31464,12 +31576,12 @@
       </c>
     </row>
     <row r="316" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A316" s="125" t="s">
-        <v>774</v>
-      </c>
-      <c r="B316" s="125"/>
-      <c r="C316" s="125"/>
-      <c r="D316" s="125"/>
+      <c r="A316" s="143" t="s">
+        <v>773</v>
+      </c>
+      <c r="B316" s="143"/>
+      <c r="C316" s="143"/>
+      <c r="D316" s="143"/>
     </row>
     <row r="317" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A317" s="13"/>
@@ -31546,7 +31658,7 @@
         <v>663</v>
       </c>
       <c r="D324" s="8" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="P324" s="9"/>
       <c r="U324" s="9"/>
@@ -31600,7 +31712,7 @@
         <v>670</v>
       </c>
       <c r="C330" s="121" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="P330" s="9"/>
       <c r="U330" s="9"/>
@@ -31736,13 +31848,13 @@
         <v>691</v>
       </c>
       <c r="C345" s="83" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="V345" s="8"/>
     </row>
     <row r="346" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A346" s="82" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B346" s="67"/>
       <c r="C346" s="67"/>
@@ -31755,7 +31867,7 @@
     </row>
     <row r="348" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C348" s="69" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="349" spans="1:22" x14ac:dyDescent="0.3">
@@ -31799,7 +31911,7 @@
     </row>
     <row r="355" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A355" s="73" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B355" s="75" t="s">
         <v>700</v>
@@ -31809,32 +31921,32 @@
     </row>
     <row r="356" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A356" s="69" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B356" s="69" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C356" s="69" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D356" s="69" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="357" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A357" s="69" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C357" s="85" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D357" s="69" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="358" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A358" s="73" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C358" s="85"/>
       <c r="D358" s="69"/>
@@ -31842,7 +31954,7 @@
     <row r="359" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A359" s="69"/>
       <c r="C359" s="85" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D359" s="69"/>
     </row>
@@ -31867,16 +31979,16 @@
     </row>
     <row r="361" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A361" s="74" t="s">
+        <v>798</v>
+      </c>
+      <c r="C361" s="83" t="s">
         <v>799</v>
-      </c>
-      <c r="C361" s="83" t="s">
-        <v>800</v>
       </c>
       <c r="V361" s="8"/>
     </row>
     <row r="362" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A362" s="86" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B362" s="67"/>
       <c r="C362" s="67"/>
@@ -31889,34 +32001,34 @@
     </row>
     <row r="364" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B364" s="85" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C364" s="85" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="365" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A365" s="69" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C365" s="69" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="366" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A366" s="69" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C366" s="69" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="367" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A367" s="70" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B367" s="69" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C367" s="85" t="s">
         <v>462</v>
@@ -31943,7 +32055,7 @@
         <v>424</v>
       </c>
       <c r="C371" s="85" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="372" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
@@ -31968,33 +32080,33 @@
         <v>431</v>
       </c>
       <c r="D374" s="91" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="F374" s="96"/>
     </row>
     <row r="375" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="B375" s="88" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C375" s="93" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="F375" s="96"/>
     </row>
     <row r="376" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A376" s="8"/>
       <c r="B376" s="87" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C376" s="93" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="D376" s="90"/>
       <c r="F376" s="96"/>
     </row>
     <row r="377" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A377" s="97" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B377" s="90"/>
       <c r="C377" s="93"/>
@@ -32005,58 +32117,58 @@
       <c r="A378" s="90"/>
       <c r="B378" s="90"/>
       <c r="C378" s="93" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="D378" s="90"/>
       <c r="F378" s="96"/>
     </row>
     <row r="379" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A379" s="93" t="s">
+        <v>852</v>
+      </c>
+      <c r="B379" s="93" t="s">
+        <v>855</v>
+      </c>
+      <c r="C379" s="93" t="s">
+        <v>854</v>
+      </c>
+      <c r="D379" s="98" t="s">
         <v>853</v>
-      </c>
-      <c r="B379" s="93" t="s">
-        <v>856</v>
-      </c>
-      <c r="C379" s="93" t="s">
-        <v>855</v>
-      </c>
-      <c r="D379" s="98" t="s">
-        <v>854</v>
       </c>
       <c r="F379" s="96"/>
     </row>
     <row r="380" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A380" s="93" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B380" s="93" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C380" s="93" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="D380" s="98" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F380" s="96"/>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A381" s="71" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="382" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A382" s="72" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B382" s="93"/>
       <c r="C382" s="80" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="383" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A383" s="69" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B383" s="8" t="s">
         <v>704</v>
@@ -32065,17 +32177,17 @@
         <v>705</v>
       </c>
       <c r="D383" s="74" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A384" s="72" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="385" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A385" s="69" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B385" s="8" t="s">
         <v>706</v>
@@ -32095,12 +32207,12 @@
     </row>
     <row r="387" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A387" s="72" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="388" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A388" s="69" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B388" s="8" t="s">
         <v>708</v>
@@ -32111,15 +32223,15 @@
     </row>
     <row r="389" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A389" s="73" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="390" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A390" s="69" t="s">
+        <v>766</v>
+      </c>
+      <c r="B390" s="69" t="s">
         <v>767</v>
-      </c>
-      <c r="B390" s="69" t="s">
-        <v>768</v>
       </c>
       <c r="C390" s="69" t="s">
         <v>477</v>
@@ -32127,16 +32239,16 @@
     </row>
     <row r="391" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A391" s="56" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="392" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A392" s="8"/>
       <c r="B392" s="93" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C392" s="8" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="393" spans="1:22" x14ac:dyDescent="0.3">
@@ -32165,22 +32277,22 @@
     </row>
     <row r="395" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A395" s="74" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C395" s="92" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="V395" s="8"/>
     </row>
     <row r="396" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A396" s="95" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C396" s="56" t="s">
+        <v>826</v>
+      </c>
+      <c r="D396" s="94" t="s">
         <v>827</v>
-      </c>
-      <c r="D396" s="94" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="397" spans="1:22" ht="187.2" x14ac:dyDescent="0.3">
@@ -32192,39 +32304,39 @@
         <v>482</v>
       </c>
       <c r="D397" s="8" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="398" spans="1:22" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A398" s="8" t="s">
+        <v>829</v>
+      </c>
+      <c r="B398" s="8" t="s">
         <v>830</v>
-      </c>
-      <c r="B398" s="8" t="s">
-        <v>831</v>
       </c>
       <c r="C398" s="8" t="s">
         <v>482</v>
       </c>
       <c r="D398" s="8" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="399" spans="1:22" ht="288" x14ac:dyDescent="0.3">
       <c r="A399" s="8"/>
       <c r="B399" s="8" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C399" s="8" t="s">
         <v>482</v>
       </c>
       <c r="D399" s="8" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="400" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A400" s="8"/>
       <c r="D400" s="8" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="401" spans="1:22" ht="244.8" x14ac:dyDescent="0.3">
@@ -32232,27 +32344,27 @@
         <v>490</v>
       </c>
       <c r="B401" s="93" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C401" s="8" t="s">
         <v>482</v>
       </c>
       <c r="D401" s="8" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="402" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A402" s="8" t="s">
+        <v>836</v>
+      </c>
+      <c r="B402" s="8" t="s">
         <v>837</v>
       </c>
-      <c r="B402" s="8" t="s">
+      <c r="C402" s="8" t="s">
         <v>838</v>
       </c>
-      <c r="C402" s="8" t="s">
+      <c r="D402" s="8" t="s">
         <v>839</v>
-      </c>
-      <c r="D402" s="8" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="403" spans="1:22" ht="216" x14ac:dyDescent="0.3">
@@ -32260,7 +32372,7 @@
         <v>497</v>
       </c>
       <c r="B403" s="93" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C403" s="8" t="s">
         <v>499</v>
@@ -32278,7 +32390,7 @@
     </row>
     <row r="405" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A405" s="8" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B405" s="8" t="s">
         <v>503</v>
@@ -32325,124 +32437,124 @@
     </row>
     <row r="409" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A409" s="74" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C409" s="83" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="V409" s="8"/>
     </row>
     <row r="410" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A410" s="82" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D410" s="74" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="411" spans="1:22" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="B411" s="93" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C411" s="93" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="D411" s="93" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="412" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A412" s="93" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B412" s="93" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C412" s="93"/>
       <c r="D412" s="70"/>
     </row>
     <row r="413" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A413" s="93" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B413" s="93" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C413" s="93" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="D413" s="70"/>
     </row>
     <row r="414" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A414" s="93" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B414" s="93"/>
       <c r="C414" s="93" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D414" s="70"/>
     </row>
     <row r="415" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A415" s="93" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B415" s="93"/>
       <c r="C415" s="93" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D415" s="70"/>
     </row>
     <row r="416" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A416" s="73" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B416" s="75" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C416" s="79" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D416" s="78" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="417" spans="1:22" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A417" s="80" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C417" s="8" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="418" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A418" s="73" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="419" spans="1:22" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A419" s="8"/>
       <c r="B419" s="85" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C419" s="89" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="420" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A420" s="81" t="s">
+        <v>792</v>
+      </c>
+      <c r="D420" s="74" t="s">
         <v>793</v>
-      </c>
-      <c r="D420" s="74" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="421" spans="1:22" ht="201.6" x14ac:dyDescent="0.3">
       <c r="B421" s="80" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C421" s="80" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="422" spans="1:22" x14ac:dyDescent="0.3">
@@ -32466,16 +32578,16 @@
     </row>
     <row r="423" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A423" s="74" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C423" s="100" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="V423" s="8"/>
     </row>
     <row r="424" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A424" s="101" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C424" s="9"/>
       <c r="V424" s="8"/>
@@ -32483,25 +32595,25 @@
     <row r="425" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B425" s="80"/>
       <c r="C425" s="93" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="426" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B426" s="80"/>
       <c r="C426" s="93" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="427" spans="1:22" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A427" s="98" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B427" s="80"/>
       <c r="C427" s="93" t="s">
+        <v>869</v>
+      </c>
+      <c r="D427" s="99" t="s">
         <v>870</v>
-      </c>
-      <c r="D427" s="99" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="428" spans="1:22" x14ac:dyDescent="0.3">
@@ -32529,96 +32641,96 @@
     </row>
     <row r="430" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A430" s="74" t="s">
+        <v>806</v>
+      </c>
+      <c r="C430" s="83" t="s">
         <v>807</v>
-      </c>
-      <c r="C430" s="83" t="s">
-        <v>808</v>
       </c>
       <c r="V430" s="8"/>
     </row>
     <row r="431" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C431" s="80" t="s">
+        <v>808</v>
+      </c>
+      <c r="D431" s="74" t="s">
         <v>809</v>
-      </c>
-      <c r="D431" s="74" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="432" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A432" s="68" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A433" s="105" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D433" s="9" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="434" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A434" s="104" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B434" s="104" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C434" s="104" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D434" s="104" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A435" s="105" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D435" s="102" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="436" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B436" s="104" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C436" s="104" t="s">
+        <v>878</v>
+      </c>
+      <c r="D436" s="104" t="s">
         <v>879</v>
-      </c>
-      <c r="D436" s="104" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A437" s="105" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="438" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
       <c r="B438" s="104" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C438" s="104" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A439" s="105" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="440" spans="1:4" ht="216" x14ac:dyDescent="0.3">
       <c r="B440" s="104" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C440" s="104" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A441" s="106" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B441" s="104"/>
       <c r="C441" s="104"/>
@@ -32627,62 +32739,62 @@
     <row r="442" spans="1:4" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A442" s="104"/>
       <c r="B442" s="104" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C442" s="104" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D442" s="104"/>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A443" s="107" t="s">
+        <v>895</v>
+      </c>
+      <c r="D443" s="9" t="s">
         <v>896</v>
-      </c>
-      <c r="D443" s="9" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="444" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
       <c r="C444" s="104" t="s">
+        <v>897</v>
+      </c>
+      <c r="D444" s="104" t="s">
         <v>898</v>
-      </c>
-      <c r="D444" s="104" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="445" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A445" s="106" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="446" spans="1:4" ht="216" x14ac:dyDescent="0.3">
       <c r="A446" s="104" t="s">
+        <v>906</v>
+      </c>
+      <c r="B446" s="104" t="s">
+        <v>904</v>
+      </c>
+      <c r="C446" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="B446" s="104" t="s">
+      <c r="D446" s="104" t="s">
         <v>905</v>
-      </c>
-      <c r="C446" s="104" t="s">
-        <v>908</v>
-      </c>
-      <c r="D446" s="104" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="447" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A447" s="106" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="448" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
       <c r="B448" s="104" t="s">
+        <v>902</v>
+      </c>
+      <c r="C448" s="104" t="s">
+        <v>901</v>
+      </c>
+      <c r="D448" s="104" t="s">
         <v>903</v>
-      </c>
-      <c r="C448" s="104" t="s">
-        <v>902</v>
-      </c>
-      <c r="D448" s="104" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="455" spans="1:22" x14ac:dyDescent="0.3">
@@ -32706,16 +32818,16 @@
     </row>
     <row r="456" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A456" s="102" t="s">
+        <v>872</v>
+      </c>
+      <c r="C456" s="103" t="s">
         <v>873</v>
-      </c>
-      <c r="C456" s="103" t="s">
-        <v>874</v>
       </c>
       <c r="V456" s="8"/>
     </row>
     <row r="457" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B457" s="108" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
   </sheetData>
@@ -32739,404 +32851,404 @@
   <dimension ref="A2:V38"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="46.109375" style="131" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="62.88671875" style="132" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.109375" style="137" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="131" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" style="127" customWidth="1"/>
-    <col min="6" max="6" width="43.33203125" style="131" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="132" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="131" customWidth="1"/>
-    <col min="9" max="9" width="64.44140625" style="131" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" style="131" customWidth="1"/>
-    <col min="11" max="11" width="39.33203125" style="131" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="131" customWidth="1"/>
-    <col min="13" max="13" width="72.5546875" style="131" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="131" customWidth="1"/>
-    <col min="15" max="15" width="7.88671875" style="131" customWidth="1"/>
-    <col min="16" max="16" width="56.88671875" style="132" customWidth="1"/>
-    <col min="17" max="17" width="46.6640625" style="132" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="132" customWidth="1"/>
-    <col min="19" max="19" width="49.109375" style="131" customWidth="1"/>
-    <col min="20" max="20" width="8.6640625" style="135"/>
-    <col min="21" max="21" width="67.6640625" style="132" customWidth="1"/>
-    <col min="22" max="22" width="68.44140625" style="131" customWidth="1"/>
-    <col min="23" max="24" width="59.44140625" style="131" customWidth="1"/>
-    <col min="25" max="25" width="59.5546875" style="131" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="131" customWidth="1"/>
-    <col min="27" max="27" width="41.33203125" style="131" customWidth="1"/>
-    <col min="28" max="16384" width="8.6640625" style="131"/>
+    <col min="1" max="1" width="46.109375" style="128" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62.88671875" style="129" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="134" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="128" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="124" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="128" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="129" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="128" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="128" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="128" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="128" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="128" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="128" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="128" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="128" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="129" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="129" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="129" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="128" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="132"/>
+    <col min="21" max="21" width="67.6640625" style="129" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="128" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="128" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="128" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="128" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="128" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="128"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22" s="127" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="128"/>
-      <c r="C2" s="129"/>
-      <c r="G2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="128"/>
-      <c r="R2" s="128"/>
-      <c r="S2" s="128"/>
-      <c r="T2" s="130"/>
-      <c r="U2" s="128"/>
+    <row r="2" spans="1:22" s="124" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="125"/>
+      <c r="C2" s="126"/>
+      <c r="G2" s="125"/>
+      <c r="P2" s="125"/>
+      <c r="Q2" s="125"/>
+      <c r="R2" s="125"/>
+      <c r="S2" s="125"/>
+      <c r="T2" s="127"/>
+      <c r="U2" s="125"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="C3" s="133" t="s">
+      <c r="C3" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="D3" s="131" t="s">
         <v>943</v>
       </c>
-      <c r="D3" s="134" t="s">
+      <c r="P3" s="128"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="129"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="133" t="s">
         <v>944</v>
       </c>
-      <c r="P3" s="131"/>
-      <c r="U3" s="131"/>
-      <c r="V3" s="132"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" s="136" t="s">
+      <c r="D4" s="131" t="s">
         <v>945</v>
       </c>
-      <c r="D4" s="134" t="s">
+    </row>
+    <row r="5" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="129"/>
+      <c r="B5" s="134" t="s">
         <v>946</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="132"/>
-      <c r="B5" s="137" t="s">
+      <c r="C5" s="134" t="s">
         <v>947</v>
       </c>
-      <c r="C5" s="137" t="s">
+    </row>
+    <row r="6" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="135" t="s">
         <v>948</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="138" t="s">
+      <c r="B6" s="134"/>
+      <c r="C6" s="134" t="s">
         <v>949</v>
       </c>
-      <c r="B6" s="137"/>
-      <c r="C6" s="137" t="s">
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="129"/>
+      <c r="B7" s="133" t="s">
         <v>950</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" s="132"/>
-      <c r="B7" s="136" t="s">
+      <c r="C7" s="133" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="134" t="s">
         <v>951</v>
       </c>
-      <c r="C7" s="136" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="137" t="s">
+      <c r="B8" s="134" t="s">
         <v>952</v>
       </c>
-      <c r="B8" s="137" t="s">
+      <c r="C8" s="134" t="s">
         <v>953</v>
       </c>
-      <c r="C8" s="137" t="s">
+    </row>
+    <row r="9" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="134"/>
+      <c r="B9" s="129" t="s">
         <v>954</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" s="137"/>
-      <c r="B9" s="132" t="s">
+      <c r="C9" s="134" t="s">
         <v>955</v>
       </c>
-      <c r="C9" s="137" t="s">
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="135" t="s">
         <v>956</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="138" t="s">
+      <c r="B10" s="134"/>
+      <c r="C10" s="134" t="s">
         <v>957</v>
       </c>
-      <c r="B10" s="137"/>
-      <c r="C10" s="137" t="s">
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="129"/>
+      <c r="B11" s="133" t="s">
+        <v>950</v>
+      </c>
+      <c r="C11" s="133" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="128" t="s">
         <v>958</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" s="132"/>
-      <c r="B11" s="136" t="s">
-        <v>951</v>
-      </c>
-      <c r="C11" s="136" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="131" t="s">
+      <c r="B12" s="129" t="s">
         <v>959</v>
       </c>
-      <c r="B12" s="132" t="s">
+      <c r="C12" s="129" t="s">
         <v>960</v>
       </c>
-      <c r="C12" s="132" t="s">
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="128" t="s">
         <v>961</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="131" t="s">
+      <c r="B13" s="129" t="s">
         <v>962</v>
       </c>
-      <c r="B13" s="132" t="s">
+      <c r="C13" s="129" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="128" t="s">
         <v>963</v>
       </c>
-      <c r="C13" s="132" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" s="131" t="s">
+      <c r="B14" s="129" t="s">
         <v>964</v>
       </c>
-      <c r="B14" s="132" t="s">
+      <c r="C14" s="129" t="s">
         <v>965</v>
       </c>
-      <c r="C14" s="132" t="s">
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="128" t="s">
         <v>966</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" s="131" t="s">
+      <c r="B15" s="129" t="s">
         <v>967</v>
       </c>
-      <c r="B15" s="132" t="s">
+      <c r="C15" s="129" t="s">
         <v>968</v>
       </c>
-      <c r="C15" s="132" t="s">
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="128" t="s">
         <v>969</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A16" s="131" t="s">
+      <c r="B16" s="129" t="s">
         <v>970</v>
       </c>
-      <c r="B16" s="132" t="s">
+      <c r="C16" s="129" t="s">
         <v>971</v>
       </c>
-      <c r="C16" s="132" t="s">
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A17" s="128" t="s">
         <v>972</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A17" s="131" t="s">
+      <c r="B17" s="129" t="s">
         <v>973</v>
       </c>
-      <c r="B17" s="132" t="s">
+      <c r="C17" s="129" t="s">
         <v>974</v>
       </c>
-      <c r="C17" s="132" t="s">
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A18" s="128" t="s">
+        <v>558</v>
+      </c>
+      <c r="B18" s="129" t="s">
         <v>975</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A18" s="131" t="s">
-        <v>558</v>
-      </c>
-      <c r="B18" s="132" t="s">
+      <c r="C18" s="129" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A19" s="128" t="s">
         <v>976</v>
       </c>
-      <c r="C18" s="132" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A19" s="131" t="s">
+      <c r="B19" s="129" t="s">
         <v>977</v>
       </c>
-      <c r="B19" s="132" t="s">
+      <c r="C19" s="129" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A20" s="128" t="s">
         <v>978</v>
       </c>
-      <c r="C19" s="132" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A20" s="131" t="s">
+      <c r="B20" s="129" t="s">
         <v>979</v>
       </c>
-      <c r="B20" s="132" t="s">
+      <c r="C20" s="129" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B21" s="129" t="s">
         <v>980</v>
       </c>
-      <c r="C20" s="132" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B21" s="132" t="s">
+      <c r="C21" s="129" t="s">
         <v>981</v>
       </c>
-      <c r="C21" s="132" t="s">
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A22" s="128" t="s">
         <v>982</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A22" s="131" t="s">
+      <c r="B22" s="129" t="s">
         <v>983</v>
       </c>
-      <c r="B22" s="132" t="s">
+      <c r="C22" s="129" t="s">
         <v>984</v>
       </c>
-      <c r="C22" s="132" t="s">
+    </row>
+    <row r="23" spans="1:21" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="134" t="s">
         <v>985</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="137" t="s">
+      <c r="B23" s="134" t="s">
         <v>986</v>
       </c>
-      <c r="B23" s="137" t="s">
+      <c r="C23" s="134" t="s">
         <v>987</v>
       </c>
-      <c r="C23" s="137" t="s">
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A24" s="136" t="s">
         <v>988</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A24" s="139" t="s">
+      <c r="B24" s="137" t="s">
         <v>989</v>
       </c>
-      <c r="B24" s="140" t="s">
+      <c r="C24" s="137" t="s">
+        <v>988</v>
+      </c>
+      <c r="D24" s="138" t="s">
         <v>990</v>
       </c>
-      <c r="C24" s="140" t="s">
-        <v>989</v>
-      </c>
-      <c r="D24" s="141" t="s">
+    </row>
+    <row r="25" spans="1:21" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A25" s="134" t="s">
         <v>991</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A25" s="137" t="s">
+      <c r="B25" s="134" t="s">
         <v>992</v>
       </c>
-      <c r="B25" s="137" t="s">
+      <c r="C25" s="134" t="s">
         <v>993</v>
       </c>
-      <c r="C25" s="137" t="s">
+      <c r="D25" s="129" t="s">
         <v>994</v>
       </c>
-      <c r="D25" s="132" t="s">
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A26" s="134"/>
+      <c r="B26" s="134"/>
+    </row>
+    <row r="27" spans="1:21" s="124" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="125"/>
+      <c r="C27" s="126"/>
+      <c r="G27" s="125"/>
+      <c r="P27" s="125"/>
+      <c r="Q27" s="125"/>
+      <c r="R27" s="125"/>
+      <c r="S27" s="125"/>
+      <c r="T27" s="127"/>
+      <c r="U27" s="125"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A28" s="129"/>
+      <c r="B28" s="134"/>
+      <c r="C28" s="130" t="s">
         <v>995</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A26" s="137"/>
-      <c r="B26" s="137"/>
-    </row>
-    <row r="27" spans="1:21" s="127" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="128"/>
-      <c r="C27" s="129"/>
-      <c r="G27" s="128"/>
-      <c r="P27" s="128"/>
-      <c r="Q27" s="128"/>
-      <c r="R27" s="128"/>
-      <c r="S27" s="128"/>
-      <c r="T27" s="130"/>
-      <c r="U27" s="128"/>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A28" s="132"/>
-      <c r="B28" s="137"/>
-      <c r="C28" s="133" t="s">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A29" s="133" t="s">
         <v>996</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A29" s="136" t="s">
+      <c r="B29" s="134"/>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A30" s="129"/>
+      <c r="B30" s="133" t="s">
+        <v>928</v>
+      </c>
+      <c r="C30" s="133" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="139" t="s">
         <v>997</v>
       </c>
-      <c r="B29" s="137"/>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A30" s="132"/>
-      <c r="B30" s="136" t="s">
-        <v>929</v>
-      </c>
-      <c r="C30" s="136" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="142" t="s">
+      <c r="B31" s="129" t="s">
         <v>998</v>
       </c>
-      <c r="B31" s="132" t="s">
+      <c r="C31" s="128" t="s">
         <v>999</v>
       </c>
-      <c r="C31" s="131" t="s">
+    </row>
+    <row r="32" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="139" t="s">
+        <v>997</v>
+      </c>
+      <c r="B32" s="129" t="s">
         <v>1000</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="142" t="s">
-        <v>998</v>
-      </c>
-      <c r="B32" s="132" t="s">
+      <c r="C32" s="128" t="s">
         <v>1001</v>
       </c>
-      <c r="C32" s="131" t="s">
+    </row>
+    <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="139" t="s">
+        <v>997</v>
+      </c>
+      <c r="B33" s="129" t="s">
         <v>1002</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="142" t="s">
-        <v>998</v>
-      </c>
-      <c r="B33" s="132" t="s">
+      <c r="C33" s="134" t="s">
         <v>1003</v>
       </c>
-      <c r="C33" s="137" t="s">
+    </row>
+    <row r="34" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="139" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="142" t="s">
+      <c r="B34" s="129" t="s">
         <v>1005</v>
       </c>
-      <c r="B34" s="132" t="s">
+      <c r="C34" s="134" t="s">
         <v>1006</v>
       </c>
-      <c r="C34" s="137" t="s">
+    </row>
+    <row r="35" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="139" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B35" s="129" t="s">
         <v>1007</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="142" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B35" s="132" t="s">
+      <c r="C35" s="134" t="s">
         <v>1008</v>
       </c>
-      <c r="C35" s="137" t="s">
+    </row>
+    <row r="36" spans="1:3" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="139" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B36" s="129" t="s">
         <v>1009</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="142" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B36" s="132" t="s">
+      <c r="C36" s="134" t="s">
         <v>1010</v>
       </c>
-      <c r="C36" s="137" t="s">
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="136" t="s">
+        <v>988</v>
+      </c>
+      <c r="C37" s="137" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="B38" s="134" t="s">
+        <v>991</v>
+      </c>
+      <c r="C38" s="129" t="s">
         <v>1011</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="139" t="s">
-        <v>989</v>
-      </c>
-      <c r="C37" s="140" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="B38" s="137" t="s">
-        <v>992</v>
-      </c>
-      <c r="C38" s="132" t="s">
-        <v>1012</v>
       </c>
     </row>
   </sheetData>
@@ -33155,7 +33267,7 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V33"/>
+  <dimension ref="A1:V35"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -33188,305 +33300,319 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="124"/>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
+      <c r="A1" s="140"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="U2" s="6"/>
+      <c r="A2" s="140"/>
+      <c r="B2" s="146" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="140"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" s="118" t="s">
-        <v>927</v>
-      </c>
-      <c r="B3" s="119"/>
-      <c r="C3" s="120" t="s">
+      <c r="A3" s="140"/>
+      <c r="B3" s="140"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="U4" s="6"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" s="118" t="s">
         <v>926</v>
       </c>
-      <c r="D3" s="118"/>
-      <c r="P3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="2"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="P4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="2"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
-        <v>709</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>710</v>
-      </c>
+      <c r="B5" s="119"/>
+      <c r="C5" s="120" t="s">
+        <v>925</v>
+      </c>
+      <c r="D5" s="118"/>
       <c r="P5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="2"/>
     </row>
-    <row r="6" spans="1:22" ht="144" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="D6" s="114" t="s">
-        <v>919</v>
-      </c>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="P6" s="1"/>
       <c r="U6" s="1"/>
       <c r="V6" s="2"/>
     </row>
-    <row r="7" spans="1:22" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>713</v>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
+        <v>709</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="D7" s="114"/>
+        <v>710</v>
+      </c>
       <c r="P7" s="1"/>
       <c r="U7" s="1"/>
       <c r="V7" s="2"/>
     </row>
-    <row r="8" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>716</v>
+    <row r="8" spans="1:22" ht="144" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>711</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>717</v>
+        <v>712</v>
+      </c>
+      <c r="D8" s="114" t="s">
+        <v>918</v>
       </c>
       <c r="P8" s="1"/>
       <c r="U8" s="1"/>
       <c r="V8" s="2"/>
     </row>
-    <row r="9" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:22" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="D9" s="114"/>
+      <c r="P9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="2"/>
+    </row>
+    <row r="10" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="P10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="2"/>
+    </row>
+    <row r="11" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
         <v>718</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B11" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="1"/>
+    </row>
+    <row r="12" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="D12" s="117" t="s">
         <v>924</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="1"/>
-    </row>
-    <row r="10" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    </row>
+    <row r="13" spans="1:22" ht="144" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="144" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>723</v>
+      </c>
+      <c r="D14" s="114" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="D10" s="117" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="144" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="144" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
-        <v>723</v>
-      </c>
-      <c r="D12" s="114" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B15" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
+        <v>726</v>
+      </c>
+      <c r="B17" s="145" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="B14" s="1"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="C18" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="C20" s="141" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D20" s="123" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>729</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="D18" s="123" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>732</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
+      <c r="B23" s="2" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="144" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="C23" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C24" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C22" s="2" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
+      <c r="B26" s="113" t="s">
+        <v>916</v>
+      </c>
+      <c r="C26" s="112" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
         <v>739</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="B24" s="113" t="s">
-        <v>917</v>
-      </c>
-      <c r="C24" s="112" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="144" x14ac:dyDescent="0.3">
-      <c r="B25" s="2" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="10" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="113" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" s="113" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="10" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B31" s="109" t="s">
+        <v>909</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B29" s="109" t="s">
-        <v>910</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="C30" s="2" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="110" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B32" s="109" t="s">
-        <v>912</v>
-      </c>
+    <row r="32" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C32" s="2" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="33" spans="3:3" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="C33" s="2" t="s">
-        <v>743</v>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="110" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B34" s="109" t="s">
+        <v>911</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="C35" s="2" t="s">
+        <v>742</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" location="/Array" xr:uid="{8115CF20-9CC3-4567-BFB8-07067DD7531F}"/>
+    <hyperlink ref="C5" r:id="rId1" location="/Array" xr:uid="{8115CF20-9CC3-4567-BFB8-07067DD7531F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
@@ -33562,7 +33688,7 @@
     </row>
     <row r="5" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>235</v>
@@ -33576,7 +33702,7 @@
     </row>
     <row r="6" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>235</v>
@@ -33585,7 +33711,7 @@
     </row>
     <row r="7" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>235</v>
@@ -33600,62 +33726,62 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C12" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
   </sheetData>
@@ -33703,12 +33829,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
-        <v>759</v>
-      </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
+      <c r="A1" s="144" t="s">
+        <v>758</v>
+      </c>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
